--- a/Templates/Exception Report (Default).xlsx
+++ b/Templates/Exception Report (Default).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delascasascp-my.sharepoint.com/personal/ro_delascasascp_com/Documents/DLC2P Server/AA Personal/Stefanos/Data Science/Python Projects/CIS Data to Google Earth (Real Time)/Templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delascasascp-my.sharepoint.com/personal/ro_delascasascp_com/Documents/DLC2P Server/AA Personal/Stefanos/Data Science/Projects (Python)/CIS Data to Google Earth (Real Time)/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="8_{0DAEB379-C59D-9A41-861D-6FBFF0BCABED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{344E71BF-18B4-F54C-80FC-FBCD6C21E78E}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="8_{0DAEB379-C59D-9A41-861D-6FBFF0BCABED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAA28E0B-E1A3-0149-BBA3-BA143B9479F4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="600" windowWidth="51120" windowHeight="26620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -68,6 +68,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -290,7 +293,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -329,6 +332,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -696,24 +702,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
@@ -726,14 +732,14 @@
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="27" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="27" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="3"/>
@@ -744,12 +750,12 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="3"/>
       <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="26"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="6"/>
       <c r="F5" s="5" t="s">
         <v>9</v>
@@ -768,20 +774,20 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21" t="s">
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="25" t="s">
         <v>3</v>
       </c>
     </row>
@@ -804,8 +810,8 @@
       <c r="F8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="25"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
@@ -814,7 +820,9 @@
       <c r="D9" s="9"/>
       <c r="E9" s="1"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="13"/>
+      <c r="G9" s="14">
+        <v>5.2629999999999999</v>
+      </c>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -824,7 +832,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="1"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="13"/>
+      <c r="G10" s="14"/>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -834,7 +842,7 @@
       <c r="D11" s="9"/>
       <c r="E11" s="1"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="13"/>
+      <c r="G11" s="14"/>
       <c r="H11" s="12"/>
     </row>
     <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -844,7 +852,7 @@
       <c r="D12" s="9"/>
       <c r="E12" s="1"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="13"/>
+      <c r="G12" s="14"/>
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -854,7 +862,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="1"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="13"/>
+      <c r="G13" s="14"/>
       <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -864,7 +872,7 @@
       <c r="D14" s="9"/>
       <c r="E14" s="1"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="13"/>
+      <c r="G14" s="14"/>
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -874,7 +882,7 @@
       <c r="D15" s="9"/>
       <c r="E15" s="1"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="13"/>
+      <c r="G15" s="14"/>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -884,7 +892,7 @@
       <c r="D16" s="9"/>
       <c r="E16" s="1"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="13"/>
+      <c r="G16" s="14"/>
       <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -894,7 +902,7 @@
       <c r="D17" s="9"/>
       <c r="E17" s="1"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="13"/>
+      <c r="G17" s="14"/>
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -904,7 +912,7 @@
       <c r="D18" s="9"/>
       <c r="E18" s="1"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="13"/>
+      <c r="G18" s="14"/>
       <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -914,7 +922,7 @@
       <c r="D19" s="9"/>
       <c r="E19" s="1"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="13"/>
+      <c r="G19" s="14"/>
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -924,7 +932,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="1"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="13"/>
+      <c r="G20" s="14"/>
       <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -934,7 +942,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="1"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="14"/>
       <c r="H21" s="12"/>
     </row>
     <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -944,7 +952,7 @@
       <c r="D22" s="9"/>
       <c r="E22" s="1"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="13"/>
+      <c r="G22" s="14"/>
       <c r="H22" s="12"/>
     </row>
     <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -954,7 +962,7 @@
       <c r="D23" s="9"/>
       <c r="E23" s="1"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="13"/>
+      <c r="G23" s="14"/>
       <c r="H23" s="12"/>
     </row>
     <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -964,7 +972,7 @@
       <c r="D24" s="9"/>
       <c r="E24" s="1"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="13"/>
+      <c r="G24" s="14"/>
       <c r="H24" s="12"/>
     </row>
     <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -974,7 +982,7 @@
       <c r="D25" s="9"/>
       <c r="E25" s="1"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="13"/>
+      <c r="G25" s="14"/>
       <c r="H25" s="12"/>
     </row>
     <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -984,7 +992,7 @@
       <c r="D26" s="9"/>
       <c r="E26" s="1"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="13"/>
+      <c r="G26" s="14"/>
       <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -994,7 +1002,7 @@
       <c r="D27" s="9"/>
       <c r="E27" s="1"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="13"/>
+      <c r="G27" s="14"/>
       <c r="H27" s="12"/>
     </row>
     <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1004,7 +1012,7 @@
       <c r="D28" s="9"/>
       <c r="E28" s="1"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="13"/>
+      <c r="G28" s="14"/>
       <c r="H28" s="12"/>
     </row>
     <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1014,7 +1022,7 @@
       <c r="D29" s="9"/>
       <c r="E29" s="1"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="13"/>
+      <c r="G29" s="14"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1024,7 +1032,7 @@
       <c r="D30" s="9"/>
       <c r="E30" s="1"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="13"/>
+      <c r="G30" s="14"/>
       <c r="H30" s="12"/>
     </row>
     <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1034,7 +1042,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="1"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="13"/>
+      <c r="G31" s="14"/>
       <c r="H31" s="12"/>
     </row>
     <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1044,7 +1052,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="1"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="13"/>
+      <c r="G32" s="14"/>
       <c r="H32" s="12"/>
     </row>
     <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1054,7 +1062,7 @@
       <c r="D33" s="9"/>
       <c r="E33" s="1"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="13"/>
+      <c r="G33" s="14"/>
       <c r="H33" s="12"/>
     </row>
     <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1064,7 +1072,7 @@
       <c r="D34" s="9"/>
       <c r="E34" s="1"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="13"/>
+      <c r="G34" s="14"/>
       <c r="H34" s="12"/>
     </row>
     <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1074,7 +1082,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="1"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="13"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="12"/>
     </row>
     <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1084,7 +1092,7 @@
       <c r="D36" s="9"/>
       <c r="E36" s="1"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="13"/>
+      <c r="G36" s="14"/>
       <c r="H36" s="12"/>
     </row>
     <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1094,7 +1102,7 @@
       <c r="D37" s="9"/>
       <c r="E37" s="1"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="13"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="12"/>
     </row>
     <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1104,7 +1112,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="1"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="13"/>
+      <c r="G38" s="14"/>
       <c r="H38" s="12"/>
     </row>
     <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1114,7 +1122,7 @@
       <c r="D39" s="9"/>
       <c r="E39" s="1"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="13"/>
+      <c r="G39" s="14"/>
       <c r="H39" s="12"/>
     </row>
     <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1124,7 +1132,7 @@
       <c r="D40" s="9"/>
       <c r="E40" s="1"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="13"/>
+      <c r="G40" s="14"/>
       <c r="H40" s="12"/>
     </row>
     <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1134,7 +1142,7 @@
       <c r="D41" s="9"/>
       <c r="E41" s="1"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="13"/>
+      <c r="G41" s="14"/>
       <c r="H41" s="12"/>
     </row>
     <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1144,7 +1152,7 @@
       <c r="D42" s="9"/>
       <c r="E42" s="1"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="13"/>
+      <c r="G42" s="14"/>
       <c r="H42" s="12"/>
     </row>
     <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1154,7 +1162,7 @@
       <c r="D43" s="9"/>
       <c r="E43" s="1"/>
       <c r="F43" s="11"/>
-      <c r="G43" s="13"/>
+      <c r="G43" s="14"/>
       <c r="H43" s="12"/>
     </row>
     <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1164,7 +1172,7 @@
       <c r="D44" s="9"/>
       <c r="E44" s="1"/>
       <c r="F44" s="11"/>
-      <c r="G44" s="13"/>
+      <c r="G44" s="14"/>
       <c r="H44" s="12"/>
     </row>
     <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1174,7 +1182,7 @@
       <c r="D45" s="9"/>
       <c r="E45" s="1"/>
       <c r="F45" s="11"/>
-      <c r="G45" s="13"/>
+      <c r="G45" s="14"/>
       <c r="H45" s="12"/>
     </row>
     <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1184,7 +1192,7 @@
       <c r="D46" s="9"/>
       <c r="E46" s="1"/>
       <c r="F46" s="11"/>
-      <c r="G46" s="13"/>
+      <c r="G46" s="14"/>
       <c r="H46" s="12"/>
     </row>
     <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1194,7 +1202,7 @@
       <c r="D47" s="9"/>
       <c r="E47" s="1"/>
       <c r="F47" s="11"/>
-      <c r="G47" s="13"/>
+      <c r="G47" s="14"/>
       <c r="H47" s="12"/>
     </row>
     <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1204,7 +1212,7 @@
       <c r="D48" s="9"/>
       <c r="E48" s="1"/>
       <c r="F48" s="11"/>
-      <c r="G48" s="13"/>
+      <c r="G48" s="14"/>
       <c r="H48" s="12"/>
     </row>
     <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1214,7 +1222,7 @@
       <c r="D49" s="9"/>
       <c r="E49" s="1"/>
       <c r="F49" s="11"/>
-      <c r="G49" s="13"/>
+      <c r="G49" s="14"/>
       <c r="H49" s="12"/>
     </row>
     <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1224,7 +1232,7 @@
       <c r="D50" s="9"/>
       <c r="E50" s="1"/>
       <c r="F50" s="11"/>
-      <c r="G50" s="13"/>
+      <c r="G50" s="14"/>
       <c r="H50" s="12"/>
     </row>
     <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1234,7 +1242,7 @@
       <c r="D51" s="9"/>
       <c r="E51" s="1"/>
       <c r="F51" s="11"/>
-      <c r="G51" s="13"/>
+      <c r="G51" s="14"/>
       <c r="H51" s="12"/>
     </row>
     <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1244,7 +1252,7 @@
       <c r="D52" s="9"/>
       <c r="E52" s="1"/>
       <c r="F52" s="11"/>
-      <c r="G52" s="13"/>
+      <c r="G52" s="14"/>
       <c r="H52" s="12"/>
     </row>
     <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1254,7 +1262,7 @@
       <c r="D53" s="9"/>
       <c r="E53" s="1"/>
       <c r="F53" s="11"/>
-      <c r="G53" s="13"/>
+      <c r="G53" s="14"/>
       <c r="H53" s="12"/>
     </row>
     <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1264,7 +1272,7 @@
       <c r="D54" s="9"/>
       <c r="E54" s="1"/>
       <c r="F54" s="11"/>
-      <c r="G54" s="13"/>
+      <c r="G54" s="14"/>
       <c r="H54" s="12"/>
     </row>
     <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1274,7 +1282,7 @@
       <c r="D55" s="9"/>
       <c r="E55" s="1"/>
       <c r="F55" s="11"/>
-      <c r="G55" s="13"/>
+      <c r="G55" s="14"/>
       <c r="H55" s="12"/>
     </row>
     <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1284,7 +1292,7 @@
       <c r="D56" s="9"/>
       <c r="E56" s="1"/>
       <c r="F56" s="11"/>
-      <c r="G56" s="13"/>
+      <c r="G56" s="14"/>
       <c r="H56" s="12"/>
     </row>
     <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1294,7 +1302,7 @@
       <c r="D57" s="9"/>
       <c r="E57" s="1"/>
       <c r="F57" s="11"/>
-      <c r="G57" s="13"/>
+      <c r="G57" s="14"/>
       <c r="H57" s="12"/>
     </row>
     <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1304,7 +1312,7 @@
       <c r="D58" s="9"/>
       <c r="E58" s="1"/>
       <c r="F58" s="11"/>
-      <c r="G58" s="13"/>
+      <c r="G58" s="14"/>
       <c r="H58" s="12"/>
     </row>
     <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1314,7 +1322,7 @@
       <c r="D59" s="9"/>
       <c r="E59" s="1"/>
       <c r="F59" s="11"/>
-      <c r="G59" s="13"/>
+      <c r="G59" s="14"/>
       <c r="H59" s="12"/>
     </row>
     <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1324,7 +1332,7 @@
       <c r="D60" s="9"/>
       <c r="E60" s="1"/>
       <c r="F60" s="11"/>
-      <c r="G60" s="13"/>
+      <c r="G60" s="14"/>
       <c r="H60" s="12"/>
     </row>
     <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1334,7 +1342,7 @@
       <c r="D61" s="9"/>
       <c r="E61" s="1"/>
       <c r="F61" s="11"/>
-      <c r="G61" s="13"/>
+      <c r="G61" s="14"/>
       <c r="H61" s="12"/>
     </row>
     <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1344,7 +1352,7 @@
       <c r="D62" s="9"/>
       <c r="E62" s="1"/>
       <c r="F62" s="11"/>
-      <c r="G62" s="13"/>
+      <c r="G62" s="14"/>
       <c r="H62" s="12"/>
     </row>
     <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1354,7 +1362,7 @@
       <c r="D63" s="9"/>
       <c r="E63" s="1"/>
       <c r="F63" s="11"/>
-      <c r="G63" s="13"/>
+      <c r="G63" s="14"/>
       <c r="H63" s="12"/>
     </row>
     <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1364,7 +1372,7 @@
       <c r="D64" s="9"/>
       <c r="E64" s="1"/>
       <c r="F64" s="11"/>
-      <c r="G64" s="13"/>
+      <c r="G64" s="14"/>
       <c r="H64" s="12"/>
     </row>
     <row r="65" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1374,7 +1382,7 @@
       <c r="D65" s="9"/>
       <c r="E65" s="1"/>
       <c r="F65" s="11"/>
-      <c r="G65" s="13"/>
+      <c r="G65" s="14"/>
       <c r="H65" s="12"/>
     </row>
     <row r="66" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1384,7 +1392,7 @@
       <c r="D66" s="9"/>
       <c r="E66" s="1"/>
       <c r="F66" s="11"/>
-      <c r="G66" s="13"/>
+      <c r="G66" s="14"/>
       <c r="H66" s="12"/>
     </row>
     <row r="67" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1394,7 +1402,7 @@
       <c r="D67" s="9"/>
       <c r="E67" s="1"/>
       <c r="F67" s="11"/>
-      <c r="G67" s="13"/>
+      <c r="G67" s="14"/>
       <c r="H67" s="12"/>
     </row>
     <row r="68" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1404,7 +1412,7 @@
       <c r="D68" s="9"/>
       <c r="E68" s="1"/>
       <c r="F68" s="11"/>
-      <c r="G68" s="13"/>
+      <c r="G68" s="14"/>
       <c r="H68" s="12"/>
     </row>
     <row r="69" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1414,7 +1422,7 @@
       <c r="D69" s="9"/>
       <c r="E69" s="1"/>
       <c r="F69" s="11"/>
-      <c r="G69" s="13"/>
+      <c r="G69" s="14"/>
       <c r="H69" s="12"/>
     </row>
     <row r="70" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1424,7 +1432,7 @@
       <c r="D70" s="9"/>
       <c r="E70" s="1"/>
       <c r="F70" s="11"/>
-      <c r="G70" s="13"/>
+      <c r="G70" s="14"/>
       <c r="H70" s="12"/>
     </row>
     <row r="71" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1434,7 +1442,7 @@
       <c r="D71" s="9"/>
       <c r="E71" s="1"/>
       <c r="F71" s="11"/>
-      <c r="G71" s="13"/>
+      <c r="G71" s="14"/>
       <c r="H71" s="12"/>
     </row>
     <row r="72" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1444,7 +1452,7 @@
       <c r="D72" s="9"/>
       <c r="E72" s="1"/>
       <c r="F72" s="11"/>
-      <c r="G72" s="13"/>
+      <c r="G72" s="14"/>
       <c r="H72" s="12"/>
     </row>
     <row r="73" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1454,7 +1462,7 @@
       <c r="D73" s="9"/>
       <c r="E73" s="1"/>
       <c r="F73" s="11"/>
-      <c r="G73" s="13"/>
+      <c r="G73" s="14"/>
       <c r="H73" s="12"/>
     </row>
     <row r="74" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1464,7 +1472,7 @@
       <c r="D74" s="9"/>
       <c r="E74" s="1"/>
       <c r="F74" s="11"/>
-      <c r="G74" s="13"/>
+      <c r="G74" s="14"/>
       <c r="H74" s="12"/>
     </row>
     <row r="75" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1474,7 +1482,7 @@
       <c r="D75" s="9"/>
       <c r="E75" s="1"/>
       <c r="F75" s="11"/>
-      <c r="G75" s="13"/>
+      <c r="G75" s="14"/>
       <c r="H75" s="12"/>
     </row>
     <row r="76" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1484,7 +1492,7 @@
       <c r="D76" s="9"/>
       <c r="E76" s="1"/>
       <c r="F76" s="11"/>
-      <c r="G76" s="13"/>
+      <c r="G76" s="14"/>
       <c r="H76" s="12"/>
     </row>
     <row r="77" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1494,7 +1502,7 @@
       <c r="D77" s="9"/>
       <c r="E77" s="1"/>
       <c r="F77" s="11"/>
-      <c r="G77" s="13"/>
+      <c r="G77" s="14"/>
       <c r="H77" s="12"/>
     </row>
     <row r="78" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1504,7 +1512,7 @@
       <c r="D78" s="9"/>
       <c r="E78" s="1"/>
       <c r="F78" s="11"/>
-      <c r="G78" s="13"/>
+      <c r="G78" s="14"/>
       <c r="H78" s="12"/>
     </row>
     <row r="79" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1514,7 +1522,7 @@
       <c r="D79" s="9"/>
       <c r="E79" s="1"/>
       <c r="F79" s="11"/>
-      <c r="G79" s="13"/>
+      <c r="G79" s="14"/>
       <c r="H79" s="12"/>
     </row>
     <row r="80" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1524,7 +1532,7 @@
       <c r="D80" s="9"/>
       <c r="E80" s="1"/>
       <c r="F80" s="11"/>
-      <c r="G80" s="13"/>
+      <c r="G80" s="14"/>
       <c r="H80" s="12"/>
     </row>
     <row r="81" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1534,7 +1542,7 @@
       <c r="D81" s="9"/>
       <c r="E81" s="1"/>
       <c r="F81" s="11"/>
-      <c r="G81" s="13"/>
+      <c r="G81" s="14"/>
       <c r="H81" s="12"/>
     </row>
     <row r="82" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1544,7 +1552,7 @@
       <c r="D82" s="9"/>
       <c r="E82" s="1"/>
       <c r="F82" s="11"/>
-      <c r="G82" s="13"/>
+      <c r="G82" s="14"/>
       <c r="H82" s="12"/>
     </row>
     <row r="83" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1554,7 +1562,7 @@
       <c r="D83" s="9"/>
       <c r="E83" s="1"/>
       <c r="F83" s="11"/>
-      <c r="G83" s="13"/>
+      <c r="G83" s="14"/>
       <c r="H83" s="12"/>
     </row>
     <row r="84" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1564,7 +1572,7 @@
       <c r="D84" s="9"/>
       <c r="E84" s="1"/>
       <c r="F84" s="11"/>
-      <c r="G84" s="13"/>
+      <c r="G84" s="14"/>
       <c r="H84" s="12"/>
     </row>
     <row r="85" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1574,7 +1582,7 @@
       <c r="D85" s="9"/>
       <c r="E85" s="1"/>
       <c r="F85" s="11"/>
-      <c r="G85" s="13"/>
+      <c r="G85" s="14"/>
       <c r="H85" s="12"/>
     </row>
     <row r="86" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1584,7 +1592,7 @@
       <c r="D86" s="9"/>
       <c r="E86" s="1"/>
       <c r="F86" s="11"/>
-      <c r="G86" s="13"/>
+      <c r="G86" s="14"/>
       <c r="H86" s="12"/>
     </row>
     <row r="87" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1594,7 +1602,7 @@
       <c r="D87" s="9"/>
       <c r="E87" s="1"/>
       <c r="F87" s="11"/>
-      <c r="G87" s="13"/>
+      <c r="G87" s="14"/>
       <c r="H87" s="12"/>
     </row>
     <row r="88" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1604,7 +1612,7 @@
       <c r="D88" s="9"/>
       <c r="E88" s="1"/>
       <c r="F88" s="11"/>
-      <c r="G88" s="13"/>
+      <c r="G88" s="14"/>
       <c r="H88" s="12"/>
     </row>
     <row r="89" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1614,7 +1622,7 @@
       <c r="D89" s="9"/>
       <c r="E89" s="1"/>
       <c r="F89" s="11"/>
-      <c r="G89" s="13"/>
+      <c r="G89" s="14"/>
       <c r="H89" s="12"/>
     </row>
     <row r="90" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1624,7 +1632,7 @@
       <c r="D90" s="9"/>
       <c r="E90" s="1"/>
       <c r="F90" s="11"/>
-      <c r="G90" s="13"/>
+      <c r="G90" s="14"/>
       <c r="H90" s="12"/>
     </row>
     <row r="91" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1634,7 +1642,7 @@
       <c r="D91" s="9"/>
       <c r="E91" s="1"/>
       <c r="F91" s="11"/>
-      <c r="G91" s="13"/>
+      <c r="G91" s="14"/>
       <c r="H91" s="12"/>
     </row>
     <row r="92" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1644,7 +1652,7 @@
       <c r="D92" s="9"/>
       <c r="E92" s="1"/>
       <c r="F92" s="11"/>
-      <c r="G92" s="13"/>
+      <c r="G92" s="14"/>
       <c r="H92" s="12"/>
     </row>
     <row r="93" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1654,7 +1662,7 @@
       <c r="D93" s="9"/>
       <c r="E93" s="1"/>
       <c r="F93" s="11"/>
-      <c r="G93" s="13"/>
+      <c r="G93" s="14"/>
       <c r="H93" s="12"/>
     </row>
     <row r="94" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1664,7 +1672,7 @@
       <c r="D94" s="9"/>
       <c r="E94" s="1"/>
       <c r="F94" s="11"/>
-      <c r="G94" s="13"/>
+      <c r="G94" s="14"/>
       <c r="H94" s="12"/>
     </row>
     <row r="95" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1674,7 +1682,7 @@
       <c r="D95" s="9"/>
       <c r="E95" s="1"/>
       <c r="F95" s="11"/>
-      <c r="G95" s="13"/>
+      <c r="G95" s="14"/>
       <c r="H95" s="12"/>
     </row>
     <row r="96" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1684,7 +1692,7 @@
       <c r="D96" s="9"/>
       <c r="E96" s="1"/>
       <c r="F96" s="11"/>
-      <c r="G96" s="13"/>
+      <c r="G96" s="14"/>
       <c r="H96" s="12"/>
     </row>
     <row r="97" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1694,7 +1702,7 @@
       <c r="D97" s="9"/>
       <c r="E97" s="1"/>
       <c r="F97" s="11"/>
-      <c r="G97" s="13"/>
+      <c r="G97" s="14"/>
       <c r="H97" s="12"/>
     </row>
     <row r="98" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1704,7 +1712,7 @@
       <c r="D98" s="9"/>
       <c r="E98" s="1"/>
       <c r="F98" s="11"/>
-      <c r="G98" s="13"/>
+      <c r="G98" s="14"/>
       <c r="H98" s="12"/>
     </row>
     <row r="99" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1714,7 +1722,7 @@
       <c r="D99" s="9"/>
       <c r="E99" s="1"/>
       <c r="F99" s="11"/>
-      <c r="G99" s="13"/>
+      <c r="G99" s="14"/>
       <c r="H99" s="12"/>
     </row>
     <row r="100" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1724,7 +1732,7 @@
       <c r="D100" s="9"/>
       <c r="E100" s="1"/>
       <c r="F100" s="11"/>
-      <c r="G100" s="13"/>
+      <c r="G100" s="14"/>
       <c r="H100" s="12"/>
     </row>
     <row r="101" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1734,7 +1742,7 @@
       <c r="D101" s="9"/>
       <c r="E101" s="1"/>
       <c r="F101" s="11"/>
-      <c r="G101" s="13"/>
+      <c r="G101" s="14"/>
       <c r="H101" s="12"/>
     </row>
     <row r="102" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1744,7 +1752,7 @@
       <c r="D102" s="9"/>
       <c r="E102" s="1"/>
       <c r="F102" s="11"/>
-      <c r="G102" s="13"/>
+      <c r="G102" s="14"/>
       <c r="H102" s="12"/>
     </row>
     <row r="103" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1754,7 +1762,7 @@
       <c r="D103" s="9"/>
       <c r="E103" s="1"/>
       <c r="F103" s="11"/>
-      <c r="G103" s="13"/>
+      <c r="G103" s="14"/>
       <c r="H103" s="12"/>
     </row>
     <row r="104" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1764,7 +1772,7 @@
       <c r="D104" s="9"/>
       <c r="E104" s="1"/>
       <c r="F104" s="11"/>
-      <c r="G104" s="13"/>
+      <c r="G104" s="14"/>
       <c r="H104" s="12"/>
     </row>
     <row r="105" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1774,7 +1782,7 @@
       <c r="D105" s="9"/>
       <c r="E105" s="1"/>
       <c r="F105" s="11"/>
-      <c r="G105" s="13"/>
+      <c r="G105" s="14"/>
       <c r="H105" s="12"/>
     </row>
     <row r="106" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1784,7 +1792,7 @@
       <c r="D106" s="9"/>
       <c r="E106" s="1"/>
       <c r="F106" s="11"/>
-      <c r="G106" s="13"/>
+      <c r="G106" s="14"/>
       <c r="H106" s="12"/>
     </row>
     <row r="107" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1794,7 +1802,7 @@
       <c r="D107" s="9"/>
       <c r="E107" s="1"/>
       <c r="F107" s="11"/>
-      <c r="G107" s="13"/>
+      <c r="G107" s="14"/>
       <c r="H107" s="12"/>
     </row>
     <row r="108" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1804,7 +1812,7 @@
       <c r="D108" s="9"/>
       <c r="E108" s="1"/>
       <c r="F108" s="11"/>
-      <c r="G108" s="13"/>
+      <c r="G108" s="14"/>
       <c r="H108" s="12"/>
     </row>
     <row r="109" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1814,7 +1822,7 @@
       <c r="D109" s="9"/>
       <c r="E109" s="1"/>
       <c r="F109" s="11"/>
-      <c r="G109" s="13"/>
+      <c r="G109" s="14"/>
       <c r="H109" s="12"/>
     </row>
     <row r="110" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1824,7 +1832,7 @@
       <c r="D110" s="9"/>
       <c r="E110" s="1"/>
       <c r="F110" s="11"/>
-      <c r="G110" s="13"/>
+      <c r="G110" s="14"/>
       <c r="H110" s="12"/>
     </row>
     <row r="111" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1834,7 +1842,7 @@
       <c r="D111" s="9"/>
       <c r="E111" s="1"/>
       <c r="F111" s="11"/>
-      <c r="G111" s="13"/>
+      <c r="G111" s="14"/>
       <c r="H111" s="12"/>
     </row>
     <row r="112" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1844,7 +1852,7 @@
       <c r="D112" s="9"/>
       <c r="E112" s="1"/>
       <c r="F112" s="11"/>
-      <c r="G112" s="13"/>
+      <c r="G112" s="14"/>
       <c r="H112" s="12"/>
     </row>
     <row r="113" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1854,7 +1862,7 @@
       <c r="D113" s="9"/>
       <c r="E113" s="1"/>
       <c r="F113" s="11"/>
-      <c r="G113" s="13"/>
+      <c r="G113" s="14"/>
       <c r="H113" s="12"/>
     </row>
     <row r="114" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1864,7 +1872,7 @@
       <c r="D114" s="9"/>
       <c r="E114" s="1"/>
       <c r="F114" s="11"/>
-      <c r="G114" s="13"/>
+      <c r="G114" s="14"/>
       <c r="H114" s="12"/>
     </row>
     <row r="115" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1874,7 +1882,7 @@
       <c r="D115" s="9"/>
       <c r="E115" s="1"/>
       <c r="F115" s="11"/>
-      <c r="G115" s="13"/>
+      <c r="G115" s="14"/>
       <c r="H115" s="12"/>
     </row>
     <row r="116" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1884,7 +1892,7 @@
       <c r="D116" s="9"/>
       <c r="E116" s="1"/>
       <c r="F116" s="11"/>
-      <c r="G116" s="13"/>
+      <c r="G116" s="14"/>
       <c r="H116" s="12"/>
     </row>
     <row r="117" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1894,7 +1902,7 @@
       <c r="D117" s="9"/>
       <c r="E117" s="1"/>
       <c r="F117" s="11"/>
-      <c r="G117" s="13"/>
+      <c r="G117" s="14"/>
       <c r="H117" s="12"/>
     </row>
     <row r="118" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1904,7 +1912,7 @@
       <c r="D118" s="9"/>
       <c r="E118" s="1"/>
       <c r="F118" s="11"/>
-      <c r="G118" s="13"/>
+      <c r="G118" s="14"/>
       <c r="H118" s="12"/>
     </row>
     <row r="119" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1914,7 +1922,7 @@
       <c r="D119" s="9"/>
       <c r="E119" s="1"/>
       <c r="F119" s="11"/>
-      <c r="G119" s="13"/>
+      <c r="G119" s="14"/>
       <c r="H119" s="12"/>
     </row>
     <row r="120" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1924,7 +1932,7 @@
       <c r="D120" s="9"/>
       <c r="E120" s="1"/>
       <c r="F120" s="11"/>
-      <c r="G120" s="13"/>
+      <c r="G120" s="14"/>
       <c r="H120" s="12"/>
     </row>
     <row r="121" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1934,7 +1942,7 @@
       <c r="D121" s="9"/>
       <c r="E121" s="1"/>
       <c r="F121" s="11"/>
-      <c r="G121" s="13"/>
+      <c r="G121" s="14"/>
       <c r="H121" s="12"/>
     </row>
     <row r="122" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1944,7 +1952,7 @@
       <c r="D122" s="9"/>
       <c r="E122" s="1"/>
       <c r="F122" s="11"/>
-      <c r="G122" s="13"/>
+      <c r="G122" s="14"/>
       <c r="H122" s="12"/>
     </row>
     <row r="123" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1954,7 +1962,7 @@
       <c r="D123" s="9"/>
       <c r="E123" s="1"/>
       <c r="F123" s="11"/>
-      <c r="G123" s="13"/>
+      <c r="G123" s="14"/>
       <c r="H123" s="12"/>
     </row>
     <row r="124" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1964,7 +1972,7 @@
       <c r="D124" s="9"/>
       <c r="E124" s="1"/>
       <c r="F124" s="11"/>
-      <c r="G124" s="13"/>
+      <c r="G124" s="14"/>
       <c r="H124" s="12"/>
     </row>
     <row r="125" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1974,7 +1982,7 @@
       <c r="D125" s="9"/>
       <c r="E125" s="1"/>
       <c r="F125" s="11"/>
-      <c r="G125" s="13"/>
+      <c r="G125" s="14"/>
       <c r="H125" s="12"/>
     </row>
     <row r="126" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1984,7 +1992,7 @@
       <c r="D126" s="9"/>
       <c r="E126" s="1"/>
       <c r="F126" s="11"/>
-      <c r="G126" s="13"/>
+      <c r="G126" s="14"/>
       <c r="H126" s="12"/>
     </row>
     <row r="127" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1994,7 +2002,7 @@
       <c r="D127" s="9"/>
       <c r="E127" s="1"/>
       <c r="F127" s="11"/>
-      <c r="G127" s="13"/>
+      <c r="G127" s="14"/>
       <c r="H127" s="12"/>
     </row>
     <row r="128" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2004,7 +2012,7 @@
       <c r="D128" s="9"/>
       <c r="E128" s="1"/>
       <c r="F128" s="11"/>
-      <c r="G128" s="13"/>
+      <c r="G128" s="14"/>
       <c r="H128" s="12"/>
     </row>
     <row r="129" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2014,7 +2022,7 @@
       <c r="D129" s="9"/>
       <c r="E129" s="1"/>
       <c r="F129" s="11"/>
-      <c r="G129" s="13"/>
+      <c r="G129" s="14"/>
       <c r="H129" s="12"/>
     </row>
     <row r="130" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2024,7 +2032,7 @@
       <c r="D130" s="9"/>
       <c r="E130" s="1"/>
       <c r="F130" s="11"/>
-      <c r="G130" s="13"/>
+      <c r="G130" s="14"/>
       <c r="H130" s="12"/>
     </row>
     <row r="131" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2034,7 +2042,7 @@
       <c r="D131" s="9"/>
       <c r="E131" s="1"/>
       <c r="F131" s="11"/>
-      <c r="G131" s="13"/>
+      <c r="G131" s="14"/>
       <c r="H131" s="12"/>
     </row>
     <row r="132" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2044,7 +2052,7 @@
       <c r="D132" s="9"/>
       <c r="E132" s="1"/>
       <c r="F132" s="11"/>
-      <c r="G132" s="13"/>
+      <c r="G132" s="14"/>
       <c r="H132" s="12"/>
     </row>
     <row r="133" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2054,7 +2062,7 @@
       <c r="D133" s="9"/>
       <c r="E133" s="1"/>
       <c r="F133" s="11"/>
-      <c r="G133" s="13"/>
+      <c r="G133" s="14"/>
       <c r="H133" s="12"/>
     </row>
     <row r="134" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2064,7 +2072,7 @@
       <c r="D134" s="9"/>
       <c r="E134" s="1"/>
       <c r="F134" s="11"/>
-      <c r="G134" s="13"/>
+      <c r="G134" s="14"/>
       <c r="H134" s="12"/>
     </row>
     <row r="135" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2074,7 +2082,7 @@
       <c r="D135" s="9"/>
       <c r="E135" s="1"/>
       <c r="F135" s="11"/>
-      <c r="G135" s="13"/>
+      <c r="G135" s="14"/>
       <c r="H135" s="12"/>
     </row>
     <row r="136" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2084,7 +2092,7 @@
       <c r="D136" s="9"/>
       <c r="E136" s="1"/>
       <c r="F136" s="11"/>
-      <c r="G136" s="13"/>
+      <c r="G136" s="14"/>
       <c r="H136" s="12"/>
     </row>
     <row r="137" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2094,7 +2102,7 @@
       <c r="D137" s="9"/>
       <c r="E137" s="1"/>
       <c r="F137" s="11"/>
-      <c r="G137" s="13"/>
+      <c r="G137" s="14"/>
       <c r="H137" s="12"/>
     </row>
     <row r="138" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2104,7 +2112,7 @@
       <c r="D138" s="9"/>
       <c r="E138" s="1"/>
       <c r="F138" s="11"/>
-      <c r="G138" s="13"/>
+      <c r="G138" s="14"/>
       <c r="H138" s="12"/>
     </row>
     <row r="139" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2114,7 +2122,7 @@
       <c r="D139" s="9"/>
       <c r="E139" s="1"/>
       <c r="F139" s="11"/>
-      <c r="G139" s="13"/>
+      <c r="G139" s="14"/>
       <c r="H139" s="12"/>
     </row>
     <row r="140" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2124,7 +2132,7 @@
       <c r="D140" s="9"/>
       <c r="E140" s="1"/>
       <c r="F140" s="11"/>
-      <c r="G140" s="13"/>
+      <c r="G140" s="14"/>
       <c r="H140" s="12"/>
     </row>
     <row r="141" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2134,7 +2142,7 @@
       <c r="D141" s="9"/>
       <c r="E141" s="1"/>
       <c r="F141" s="11"/>
-      <c r="G141" s="13"/>
+      <c r="G141" s="14"/>
       <c r="H141" s="12"/>
     </row>
     <row r="142" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2144,7 +2152,7 @@
       <c r="D142" s="9"/>
       <c r="E142" s="1"/>
       <c r="F142" s="11"/>
-      <c r="G142" s="13"/>
+      <c r="G142" s="14"/>
       <c r="H142" s="12"/>
     </row>
     <row r="143" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2154,7 +2162,7 @@
       <c r="D143" s="9"/>
       <c r="E143" s="1"/>
       <c r="F143" s="11"/>
-      <c r="G143" s="13"/>
+      <c r="G143" s="14"/>
       <c r="H143" s="12"/>
     </row>
     <row r="144" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2164,7 +2172,7 @@
       <c r="D144" s="9"/>
       <c r="E144" s="1"/>
       <c r="F144" s="11"/>
-      <c r="G144" s="13"/>
+      <c r="G144" s="14"/>
       <c r="H144" s="12"/>
     </row>
     <row r="145" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2174,7 +2182,7 @@
       <c r="D145" s="9"/>
       <c r="E145" s="1"/>
       <c r="F145" s="11"/>
-      <c r="G145" s="13"/>
+      <c r="G145" s="14"/>
       <c r="H145" s="12"/>
     </row>
     <row r="146" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2184,7 +2192,7 @@
       <c r="D146" s="9"/>
       <c r="E146" s="1"/>
       <c r="F146" s="11"/>
-      <c r="G146" s="13"/>
+      <c r="G146" s="14"/>
       <c r="H146" s="12"/>
     </row>
     <row r="147" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2194,7 +2202,7 @@
       <c r="D147" s="9"/>
       <c r="E147" s="1"/>
       <c r="F147" s="11"/>
-      <c r="G147" s="13"/>
+      <c r="G147" s="14"/>
       <c r="H147" s="12"/>
     </row>
     <row r="148" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2204,7 +2212,7 @@
       <c r="D148" s="9"/>
       <c r="E148" s="1"/>
       <c r="F148" s="11"/>
-      <c r="G148" s="13"/>
+      <c r="G148" s="14"/>
       <c r="H148" s="12"/>
     </row>
     <row r="149" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2214,7 +2222,7 @@
       <c r="D149" s="9"/>
       <c r="E149" s="1"/>
       <c r="F149" s="11"/>
-      <c r="G149" s="13"/>
+      <c r="G149" s="14"/>
       <c r="H149" s="12"/>
     </row>
     <row r="150" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2224,7 +2232,7 @@
       <c r="D150" s="9"/>
       <c r="E150" s="1"/>
       <c r="F150" s="11"/>
-      <c r="G150" s="13"/>
+      <c r="G150" s="14"/>
       <c r="H150" s="12"/>
     </row>
     <row r="151" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2234,7 +2242,7 @@
       <c r="D151" s="9"/>
       <c r="E151" s="1"/>
       <c r="F151" s="11"/>
-      <c r="G151" s="13"/>
+      <c r="G151" s="14"/>
       <c r="H151" s="12"/>
     </row>
     <row r="152" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2244,7 +2252,7 @@
       <c r="D152" s="9"/>
       <c r="E152" s="1"/>
       <c r="F152" s="11"/>
-      <c r="G152" s="13"/>
+      <c r="G152" s="14"/>
       <c r="H152" s="12"/>
     </row>
     <row r="153" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2254,7 +2262,7 @@
       <c r="D153" s="9"/>
       <c r="E153" s="1"/>
       <c r="F153" s="11"/>
-      <c r="G153" s="13"/>
+      <c r="G153" s="14"/>
       <c r="H153" s="12"/>
     </row>
     <row r="154" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2264,7 +2272,7 @@
       <c r="D154" s="9"/>
       <c r="E154" s="1"/>
       <c r="F154" s="11"/>
-      <c r="G154" s="13"/>
+      <c r="G154" s="14"/>
       <c r="H154" s="12"/>
     </row>
     <row r="155" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2274,7 +2282,7 @@
       <c r="D155" s="9"/>
       <c r="E155" s="1"/>
       <c r="F155" s="11"/>
-      <c r="G155" s="13"/>
+      <c r="G155" s="14"/>
       <c r="H155" s="12"/>
     </row>
     <row r="156" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2284,7 +2292,7 @@
       <c r="D156" s="9"/>
       <c r="E156" s="1"/>
       <c r="F156" s="11"/>
-      <c r="G156" s="13"/>
+      <c r="G156" s="14"/>
       <c r="H156" s="12"/>
     </row>
     <row r="157" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2294,7 +2302,7 @@
       <c r="D157" s="9"/>
       <c r="E157" s="1"/>
       <c r="F157" s="11"/>
-      <c r="G157" s="13"/>
+      <c r="G157" s="14"/>
       <c r="H157" s="12"/>
     </row>
     <row r="158" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2304,7 +2312,7 @@
       <c r="D158" s="9"/>
       <c r="E158" s="1"/>
       <c r="F158" s="11"/>
-      <c r="G158" s="13"/>
+      <c r="G158" s="14"/>
       <c r="H158" s="12"/>
     </row>
     <row r="159" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2314,7 +2322,7 @@
       <c r="D159" s="9"/>
       <c r="E159" s="1"/>
       <c r="F159" s="11"/>
-      <c r="G159" s="13"/>
+      <c r="G159" s="14"/>
       <c r="H159" s="12"/>
     </row>
     <row r="160" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2324,7 +2332,7 @@
       <c r="D160" s="9"/>
       <c r="E160" s="1"/>
       <c r="F160" s="11"/>
-      <c r="G160" s="13"/>
+      <c r="G160" s="14"/>
       <c r="H160" s="12"/>
     </row>
     <row r="161" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2334,7 +2342,7 @@
       <c r="D161" s="9"/>
       <c r="E161" s="1"/>
       <c r="F161" s="11"/>
-      <c r="G161" s="13"/>
+      <c r="G161" s="14"/>
       <c r="H161" s="12"/>
     </row>
     <row r="162" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2344,7 +2352,7 @@
       <c r="D162" s="9"/>
       <c r="E162" s="1"/>
       <c r="F162" s="11"/>
-      <c r="G162" s="13"/>
+      <c r="G162" s="14"/>
       <c r="H162" s="12"/>
     </row>
     <row r="163" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2354,7 +2362,7 @@
       <c r="D163" s="9"/>
       <c r="E163" s="1"/>
       <c r="F163" s="11"/>
-      <c r="G163" s="13"/>
+      <c r="G163" s="14"/>
       <c r="H163" s="12"/>
     </row>
     <row r="164" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2364,7 +2372,7 @@
       <c r="D164" s="9"/>
       <c r="E164" s="1"/>
       <c r="F164" s="11"/>
-      <c r="G164" s="13"/>
+      <c r="G164" s="14"/>
       <c r="H164" s="12"/>
     </row>
     <row r="165" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2374,7 +2382,7 @@
       <c r="D165" s="9"/>
       <c r="E165" s="1"/>
       <c r="F165" s="11"/>
-      <c r="G165" s="13"/>
+      <c r="G165" s="14"/>
       <c r="H165" s="12"/>
     </row>
     <row r="166" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2384,7 +2392,7 @@
       <c r="D166" s="9"/>
       <c r="E166" s="1"/>
       <c r="F166" s="11"/>
-      <c r="G166" s="13"/>
+      <c r="G166" s="14"/>
       <c r="H166" s="12"/>
     </row>
     <row r="167" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2394,7 +2402,7 @@
       <c r="D167" s="9"/>
       <c r="E167" s="1"/>
       <c r="F167" s="11"/>
-      <c r="G167" s="13"/>
+      <c r="G167" s="14"/>
       <c r="H167" s="12"/>
     </row>
     <row r="168" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2404,7 +2412,7 @@
       <c r="D168" s="9"/>
       <c r="E168" s="1"/>
       <c r="F168" s="11"/>
-      <c r="G168" s="13"/>
+      <c r="G168" s="14"/>
       <c r="H168" s="12"/>
     </row>
     <row r="169" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2414,7 +2422,7 @@
       <c r="D169" s="9"/>
       <c r="E169" s="1"/>
       <c r="F169" s="11"/>
-      <c r="G169" s="13"/>
+      <c r="G169" s="14"/>
       <c r="H169" s="12"/>
     </row>
     <row r="170" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2424,7 +2432,7 @@
       <c r="D170" s="9"/>
       <c r="E170" s="1"/>
       <c r="F170" s="11"/>
-      <c r="G170" s="13"/>
+      <c r="G170" s="14"/>
       <c r="H170" s="12"/>
     </row>
     <row r="171" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2434,7 +2442,7 @@
       <c r="D171" s="9"/>
       <c r="E171" s="1"/>
       <c r="F171" s="11"/>
-      <c r="G171" s="13"/>
+      <c r="G171" s="14"/>
       <c r="H171" s="12"/>
     </row>
     <row r="172" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2444,7 +2452,7 @@
       <c r="D172" s="9"/>
       <c r="E172" s="1"/>
       <c r="F172" s="11"/>
-      <c r="G172" s="13"/>
+      <c r="G172" s="14"/>
       <c r="H172" s="12"/>
     </row>
     <row r="173" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2454,7 +2462,7 @@
       <c r="D173" s="9"/>
       <c r="E173" s="1"/>
       <c r="F173" s="11"/>
-      <c r="G173" s="13"/>
+      <c r="G173" s="14"/>
       <c r="H173" s="12"/>
     </row>
     <row r="174" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2464,7 +2472,7 @@
       <c r="D174" s="9"/>
       <c r="E174" s="1"/>
       <c r="F174" s="11"/>
-      <c r="G174" s="13"/>
+      <c r="G174" s="14"/>
       <c r="H174" s="12"/>
     </row>
     <row r="175" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2474,7 +2482,7 @@
       <c r="D175" s="9"/>
       <c r="E175" s="1"/>
       <c r="F175" s="11"/>
-      <c r="G175" s="13"/>
+      <c r="G175" s="14"/>
       <c r="H175" s="12"/>
     </row>
     <row r="176" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2484,7 +2492,7 @@
       <c r="D176" s="9"/>
       <c r="E176" s="1"/>
       <c r="F176" s="11"/>
-      <c r="G176" s="13"/>
+      <c r="G176" s="14"/>
       <c r="H176" s="12"/>
     </row>
     <row r="177" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2494,7 +2502,7 @@
       <c r="D177" s="9"/>
       <c r="E177" s="1"/>
       <c r="F177" s="11"/>
-      <c r="G177" s="13"/>
+      <c r="G177" s="14"/>
       <c r="H177" s="12"/>
     </row>
     <row r="178" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2504,7 +2512,7 @@
       <c r="D178" s="9"/>
       <c r="E178" s="1"/>
       <c r="F178" s="11"/>
-      <c r="G178" s="13"/>
+      <c r="G178" s="14"/>
       <c r="H178" s="12"/>
     </row>
     <row r="179" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2514,7 +2522,7 @@
       <c r="D179" s="9"/>
       <c r="E179" s="1"/>
       <c r="F179" s="11"/>
-      <c r="G179" s="13"/>
+      <c r="G179" s="14"/>
       <c r="H179" s="12"/>
     </row>
     <row r="180" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2524,7 +2532,7 @@
       <c r="D180" s="9"/>
       <c r="E180" s="1"/>
       <c r="F180" s="11"/>
-      <c r="G180" s="13"/>
+      <c r="G180" s="14"/>
       <c r="H180" s="12"/>
     </row>
     <row r="181" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2534,7 +2542,7 @@
       <c r="D181" s="9"/>
       <c r="E181" s="1"/>
       <c r="F181" s="11"/>
-      <c r="G181" s="13"/>
+      <c r="G181" s="14"/>
       <c r="H181" s="12"/>
     </row>
     <row r="182" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2544,7 +2552,7 @@
       <c r="D182" s="9"/>
       <c r="E182" s="1"/>
       <c r="F182" s="11"/>
-      <c r="G182" s="13"/>
+      <c r="G182" s="14"/>
       <c r="H182" s="12"/>
     </row>
     <row r="183" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2554,7 +2562,7 @@
       <c r="D183" s="9"/>
       <c r="E183" s="1"/>
       <c r="F183" s="11"/>
-      <c r="G183" s="13"/>
+      <c r="G183" s="14"/>
       <c r="H183" s="12"/>
     </row>
     <row r="184" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2564,7 +2572,7 @@
       <c r="D184" s="9"/>
       <c r="E184" s="1"/>
       <c r="F184" s="11"/>
-      <c r="G184" s="13"/>
+      <c r="G184" s="14"/>
       <c r="H184" s="12"/>
     </row>
     <row r="185" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2574,7 +2582,7 @@
       <c r="D185" s="9"/>
       <c r="E185" s="1"/>
       <c r="F185" s="11"/>
-      <c r="G185" s="13"/>
+      <c r="G185" s="14"/>
       <c r="H185" s="12"/>
     </row>
     <row r="186" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2584,7 +2592,7 @@
       <c r="D186" s="9"/>
       <c r="E186" s="1"/>
       <c r="F186" s="11"/>
-      <c r="G186" s="13"/>
+      <c r="G186" s="14"/>
       <c r="H186" s="12"/>
     </row>
     <row r="187" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2594,7 +2602,7 @@
       <c r="D187" s="9"/>
       <c r="E187" s="1"/>
       <c r="F187" s="11"/>
-      <c r="G187" s="13"/>
+      <c r="G187" s="14"/>
       <c r="H187" s="12"/>
     </row>
     <row r="188" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2604,7 +2612,7 @@
       <c r="D188" s="9"/>
       <c r="E188" s="1"/>
       <c r="F188" s="11"/>
-      <c r="G188" s="13"/>
+      <c r="G188" s="14"/>
       <c r="H188" s="12"/>
     </row>
     <row r="189" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2614,7 +2622,7 @@
       <c r="D189" s="9"/>
       <c r="E189" s="1"/>
       <c r="F189" s="11"/>
-      <c r="G189" s="13"/>
+      <c r="G189" s="14"/>
       <c r="H189" s="12"/>
     </row>
     <row r="190" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2624,7 +2632,7 @@
       <c r="D190" s="9"/>
       <c r="E190" s="1"/>
       <c r="F190" s="11"/>
-      <c r="G190" s="13"/>
+      <c r="G190" s="14"/>
       <c r="H190" s="12"/>
     </row>
     <row r="191" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2634,7 +2642,7 @@
       <c r="D191" s="9"/>
       <c r="E191" s="1"/>
       <c r="F191" s="11"/>
-      <c r="G191" s="13"/>
+      <c r="G191" s="14"/>
       <c r="H191" s="12"/>
     </row>
     <row r="192" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2644,7 +2652,7 @@
       <c r="D192" s="9"/>
       <c r="E192" s="1"/>
       <c r="F192" s="11"/>
-      <c r="G192" s="13"/>
+      <c r="G192" s="14"/>
       <c r="H192" s="12"/>
     </row>
     <row r="193" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2654,7 +2662,7 @@
       <c r="D193" s="9"/>
       <c r="E193" s="1"/>
       <c r="F193" s="11"/>
-      <c r="G193" s="13"/>
+      <c r="G193" s="14"/>
       <c r="H193" s="12"/>
     </row>
     <row r="194" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2664,7 +2672,7 @@
       <c r="D194" s="9"/>
       <c r="E194" s="1"/>
       <c r="F194" s="11"/>
-      <c r="G194" s="13"/>
+      <c r="G194" s="14"/>
       <c r="H194" s="12"/>
     </row>
     <row r="195" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2674,7 +2682,7 @@
       <c r="D195" s="9"/>
       <c r="E195" s="1"/>
       <c r="F195" s="11"/>
-      <c r="G195" s="13"/>
+      <c r="G195" s="14"/>
       <c r="H195" s="12"/>
     </row>
     <row r="196" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2684,7 +2692,7 @@
       <c r="D196" s="9"/>
       <c r="E196" s="1"/>
       <c r="F196" s="11"/>
-      <c r="G196" s="13"/>
+      <c r="G196" s="14"/>
       <c r="H196" s="12"/>
     </row>
     <row r="197" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2694,7 +2702,7 @@
       <c r="D197" s="9"/>
       <c r="E197" s="1"/>
       <c r="F197" s="11"/>
-      <c r="G197" s="13"/>
+      <c r="G197" s="14"/>
       <c r="H197" s="12"/>
     </row>
     <row r="198" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2704,7 +2712,7 @@
       <c r="D198" s="9"/>
       <c r="E198" s="1"/>
       <c r="F198" s="11"/>
-      <c r="G198" s="13"/>
+      <c r="G198" s="14"/>
       <c r="H198" s="12"/>
     </row>
     <row r="199" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2714,7 +2722,7 @@
       <c r="D199" s="9"/>
       <c r="E199" s="1"/>
       <c r="F199" s="11"/>
-      <c r="G199" s="13"/>
+      <c r="G199" s="14"/>
       <c r="H199" s="12"/>
     </row>
     <row r="200" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2724,7 +2732,7 @@
       <c r="D200" s="9"/>
       <c r="E200" s="1"/>
       <c r="F200" s="11"/>
-      <c r="G200" s="13"/>
+      <c r="G200" s="14"/>
       <c r="H200" s="12"/>
     </row>
   </sheetData>
@@ -2776,24 +2784,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
@@ -2806,14 +2814,14 @@
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="27" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="27" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="3"/>
@@ -2824,12 +2832,12 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="3"/>
       <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="26"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="6"/>
       <c r="F5" s="5" t="s">
         <v>9</v>
@@ -2848,20 +2856,20 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21" t="s">
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="25" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2884,8 +2892,8 @@
       <c r="F8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="25"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
@@ -4856,24 +4864,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
@@ -4886,14 +4894,14 @@
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="27" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="27" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="3"/>
@@ -4904,12 +4912,12 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="3"/>
       <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="26"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="6"/>
       <c r="F5" s="5" t="s">
         <v>9</v>
@@ -4928,20 +4936,20 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21" t="s">
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="25" t="s">
         <v>3</v>
       </c>
     </row>
@@ -4964,8 +4972,8 @@
       <c r="F8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="25"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
